--- a/solutions/demo/closing-engine/template_ja.xlsx
+++ b/solutions/demo/closing-engine/template_ja.xlsx
@@ -1927,17 +1927,17 @@
     <row r="3" ht="174" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>要確認の事項の番号（画面と底稿にあります）。ふつうは自動で入ります。</t>
+          <t>要確認の事項の番号（画面とワークペーパーにあります）。ふつうは自動で入ります。</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>「記帳」＝この 1 件をどの科目に入れるかを答える。「処理済み」＝別の方法で済んでいるので、もう尋ねなくてよい。</t>
+          <t>「仕訳する」＝この 1 件をどの科目に入れるかを答える。「処理済み」＝別の方法で済んでいるので、もう尋ねなくてよい。</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>「記帳」のとき：相手の科目。</t>
+          <t>「仕訳する」のとき：相手の科目。</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -2044,7 +2044,7 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B5:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="ドロップダウンから選んでください" error="この欄は、一覧から 1 つ選びます。" type="list">
-      <formula1>"記帳,処理済み"</formula1>
+      <formula1>"仕訳する,処理済み"</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='科目表'!$B$2:$B$400</formula1>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>対応する中国語の科目名。空でも構いません（中日 2 言語の底稿にだけ表示）。</t>
+          <t>対応する中国語の科目名。空でも構いません（中国語と日本語を併記するワークペーパーにだけ表示）。</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>底稿に表示する名前。氏名でも記号でも構いません。</t>
+          <t>ワークペーパーに表示する名前。氏名でも記号でも構いません。</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">

--- a/solutions/demo/closing-engine/template_ja.xlsx
+++ b/solutions/demo/closing-engine/template_ja.xlsx
@@ -1267,7 +1267,7 @@
       <c r="A1" s="7" t="inlineStr">
         <is>
           <t>この表：毎月決まって出てくる入出金（家賃・得意先の入金・手数料…）。「摘要にこの字があれば、この科目」とあらかじめ書いておくと、1 件ずつ尋ねられなくなります。
-いつ書くか：書くことを勧めますが、必須ではありません：書かなくても締められ、明細を 1 件ずつ尋ねるだけです。給与・社会保険・源泉所得税・住民税の支払と、自社の口座どうしの振替は書かなくてよい（自動で照合します）。
+いつ書くか：書くことを勧めますが、必須ではありません：書かなくても締められ、明細を 1 件ずつ尋ねるだけです。給与・社会保険・源泉所得税・住民税の支払と、自社の口座どうしの振替は書かなくてかまいません（自動で照合します）。
 書かないと：1 つのルールには 1 つの科目だけ。1 件の入出金を 2 科目に分けるもの（借入の返済＝元金＋利息、手数料を引かれた入金、源泉所得税を天引きした報酬の支払）はルールにせず、締めた後に画面でその 1 件に「回答」して分けます。</t>
         </is>
       </c>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>「仕訳する」＝この 1 件をどの科目に入れるかを答える。「処理済み」＝別の方法で済んでいるので、もう尋ねなくてよい。</t>
+          <t>「仕訳する」＝この 1 件をどの科目に入れるかを答えます。「処理済み」＝別の方法で済んでいるので、もう尋ねません。</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>「当月に計上」＝毎月末にその月分を未払費用に計上（会計基準に沿う。おすすめ）。「納付時」＝翌月末に引き落とされたときに費用にする（簡便な方法）。</t>
+          <t>「当月に計上」＝毎月末にその月分を未払費用に計上します（会計基準に沿います。おすすめ）。「納付時」＝翌月末に引き落とされたときに費用にします（簡便な方法）。</t>
         </is>
       </c>
       <c r="C10" s="9" t="n"/>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>「毎月見積計上」＝毎月の賃金から見積って未払費用に計上し、年度更新で精算（会計基準に沿う）。「納付時」＝年度更新の納付のときに一度に費用にする（金額が小さいときの簡便な方法）。</t>
+          <t>「毎月見積計上」＝毎月の賃金から見積って未払費用に計上し、年度更新で精算します（会計基準に沿います）。「納付時」＝年度更新の納付のときに一度に費用にします（金額が小さいときの簡便な方法）。</t>
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="126" customHeight="1">
+    <row r="3" ht="138" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>自分で付ける記号。ほかの表でこの人を指すのに使います。例：E01</t>
@@ -6437,7 +6437,7 @@
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>住民税の納め方。「特別徴収」＝会社が給与から天引き（このときは「住民税」の表に毎月の金額を書く）。「普通徴収」＝本人が自分で納める（会社は引かない）。</t>
+          <t>住民税の納め方。「特別徴収」＝会社が給与から天引きします（このときは「住民税」の表に毎月の金額を書きます）。「普通徴収」＝本人が自分で納めます（会社は引きません）。</t>
         </is>
       </c>
     </row>

--- a/solutions/demo/closing-engine/template_ja.xlsx
+++ b/solutions/demo/closing-engine/template_ja.xlsx
@@ -2064,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2080,8 +2080,9 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="51" customHeight="1">
@@ -2156,21 +2157,26 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
+          <t>決算整理</t>
+        </is>
+      </c>
+      <c r="N2" s="8" t="inlineStr">
+        <is>
           <t>判断者</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="O2" s="8" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="P2" s="8" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="90" customHeight="1">
+    <row r="3" ht="162" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>仕訳の番号。同じ仕訳の行には同じ番号を書きます。例：ADJ-2026-06-01</t>
@@ -2233,15 +2239,20 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
+          <t>決算整理（第 13 期）の仕訳なら「はい」。日付は決算月の末日にします。月次の損益では決算月の「当月」に入れず別の欄に出し、期首からの累計には入れます。</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
           <t>この判断をした人（氏名）。【必須】</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>判断した日。思い出せなければ、書いている今日の日付で構いません。【必須】例：2026-05-01</t>
         </is>
       </c>
-      <c r="O3" s="6" t="inlineStr">
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>なぜそう処理するか。空でも構いませんが、書いておくと後で調べやすくなります。</t>
         </is>
@@ -2310,15 +2321,20 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>by</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
@@ -2326,9 +2342,9 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="E5:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"月末"</formula1>
     </dataValidation>
@@ -2337,6 +2353,9 @@
     </dataValidation>
     <dataValidation sqref="K5:K2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"対象外,課税仕入10%,課税売上10%,非課税仕入,非課税売上"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M5:M2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="ドロップダウンから選んでください" error="この欄は、一覧から 1 つ選びます。" type="list">
+      <formula1>"はい"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/solutions/demo/closing-engine/template_ja.xlsx
+++ b/solutions/demo/closing-engine/template_ja.xlsx
@@ -1842,7 +1842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1853,9 +1853,10 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="51" customHeight="1">
@@ -1910,15 +1911,20 @@
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
+          <t>納付日</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
           <t>判断者</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
@@ -1967,15 +1973,20 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
+          <t>【明細に無い予定の納付（社保・源泉・住民税）を「処理済み」と答えるときだけ】実際に納めた日。例：2026-09-16。期限を過ぎたかどうかをこれで確かめます。</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
           <t>この判断をした人（氏名）。【必須】</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>判断した日。思い出せなければ、書いている今日の日付で構いません。【必須】例：2026-05-01</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>なぜそう処理するか。空でも構いませんが、書いておくと後で調べやすくなります。</t>
         </is>
@@ -2024,15 +2035,20 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>paid_on</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>by</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
@@ -2040,7 +2056,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B5:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="ドロップダウンから選んでください" error="この欄は、一覧から 1 つ選びます。" type="list">
